--- a/wms-vue3/public/templates/purchase-order-import-template.xlsx
+++ b/wms-vue3/public/templates/purchase-order-import-template.xlsx
@@ -1,56 +1,52 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="采购主单" sheetId="1" r:id="rId1"/>
-    <sheet name="采购明细" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="采购主单" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="采购明细" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -65,14 +61,85 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -151,7 +218,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -186,7 +252,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -221,16 +286,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -352,220 +421,415 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K2"/>
-  <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-    <col min="4" max="4" width="16.83203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
-    <col min="9" max="9" width="16.83203125" customWidth="1"/>
-    <col min="10" max="10" width="16.83203125" customWidth="1"/>
-    <col min="11" max="11" width="16.83203125" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>序号</v>
-      </c>
-      <c r="B1" t="str">
-        <v>供应商名称</v>
-      </c>
-      <c r="C1" t="str">
-        <v>订单日期</v>
-      </c>
-      <c r="D1" t="str">
-        <v>送货天数</v>
-      </c>
-      <c r="E1" t="str">
-        <v>运费承担方式</v>
-      </c>
-      <c r="F1" t="str">
-        <v>付款方式</v>
-      </c>
-      <c r="G1" t="str">
-        <v>抹零金额</v>
-      </c>
-      <c r="H1" t="str">
-        <v>使用预存款金额</v>
-      </c>
-      <c r="I1" t="str">
-        <v>使用赠送金额</v>
-      </c>
-      <c r="J1" t="str">
-        <v>预付款比例</v>
-      </c>
-      <c r="K1" t="str">
-        <v>备注</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>供应商名称</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>订单日期</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>送货天数</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>运费承担方式</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>付款方式</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>抹零金额</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>使用预存款金额</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>预付款比例</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="str">
-        <v>东方供应商</v>
-      </c>
-      <c r="C2" t="str">
-        <v>2026-08-25</v>
-      </c>
-      <c r="D2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>示例供应商A</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>7</v>
       </c>
-      <c r="E2" t="str">
-        <v>有需方承担运费</v>
-      </c>
-      <c r="F2" t="str">
-        <v>现结</v>
-      </c>
-      <c r="G2">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>有需方承担运费</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>月结</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>0</v>
       </c>
-      <c r="I2">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>主单示例行</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>示例供应商B</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>由发货方承担运费</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>预付款使用</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H3" t="n">
         <v>0</v>
       </c>
-      <c r="J2">
-        <v>100</v>
-      </c>
-      <c r="K2" t="str">
-        <v>示例备注</v>
+      <c r="I3" t="n">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K2"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I2"/>
-  <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-    <col min="4" max="4" width="16.83203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
-    <col min="9" max="9" width="16.83203125" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>主单序号</v>
-      </c>
-      <c r="B1" t="str">
-        <v>产品名称</v>
-      </c>
-      <c r="C1" t="str">
-        <v>采购单价</v>
-      </c>
-      <c r="D1" t="str">
-        <v>采购数量</v>
-      </c>
-      <c r="E1" t="str">
-        <v>发货状态</v>
-      </c>
-      <c r="F1" t="str">
-        <v>发货日期</v>
-      </c>
-      <c r="G1" t="str">
-        <v>计量单位名称</v>
-      </c>
-      <c r="H1" t="str">
-        <v>物流单号</v>
-      </c>
-      <c r="I1" t="str">
-        <v>备注</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>主单序号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>产品名称</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>规格</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>采购单价</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>采购数量</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>发货状态</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>发货日期</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>计量单位名称</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>使用赠送金额</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>物流单号</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="str">
-        <v>示例产品</v>
-      </c>
-      <c r="C2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>示例产品名称A</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>500ml</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>10.5</v>
       </c>
-      <c r="D2">
+      <c r="E2" t="n">
         <v>100</v>
       </c>
-      <c r="E2" t="str">
-        <v>未发货</v>
-      </c>
-      <c r="F2" t="str">
-        <v>2026-08-30</v>
-      </c>
-      <c r="G2" t="str">
-        <v>件</v>
-      </c>
-      <c r="H2" t="str">
-        <v/>
-      </c>
-      <c r="I2" t="str">
-        <v>示例备注</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>未发货</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>明细示例行</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>示例产品名称B</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>已发货</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>SF123456</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>示例产品名称A</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>未发货</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>填写说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1. 本文件用于批量创建采购订单：保留「采购主单」「采购明细」两个工作表的结构与标题行，将示例数据替换为真实数据后上传；本「填写说明」表上传时会被自动忽略。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2. 主单「序号」为正整数且本表内唯一；明细通过「主单序号」关联主单，必须存在于主单表；每张主单至少 1 条、至多 999 条明细。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3. 明细以「产品名称+规格」联合标识产品（规格为可选列，产品无规格则留空），须与系统内产品档案完全一致（含空格与全半角符号）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4. 日期列（订单日期/发货日期）格式 YYYY-MM-DD，建议文本格式填写（日期格式单元格亦可自动兼容）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5. 供应商须有效启用且未删除；运费承担方式/付款方式按枚举中文名称填写；付款方式为"月结"时供应商须已开通月结权限。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6. 抹零金额/使用预存款金额选填且不得为负，默认 0（意向值，审核时才实际扣款）；使用赠送金额在「采购明细」表按行填写：必填可为 0，不得超过行金额（采购单价×采购数量），主单使用赠送金额=各行之和；仅付款方式为"预付款使用"时预付款比例生效（1-100 整数）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7. 产品须有效、未停产且已绑定该供应商；同一主单下同一产品不得重复（同名不同规格可分别成行）；采购单价、采购数量必须大于 0。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8. 上次采购单价由系统自动获取，无需填写；发货状态填"未发货/已发货"或 0/1（0=未发货不会被处理为空或默认 1）；已发货时发货日期必填。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>9. 计量单位名称选填，不填取产品默认单位；单次导入上限：主单 2000 张、明细 20000 条，超限请分批上传。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10. 任一行校验失败则整批驳回（全部不落库），错误按"工作表+行号"返回全部明细。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>「规格」列为可选列：产品以「产品名称+规格」联合定位，须与产品档案完全一致（产品无规格则留空）；名称相同但规格组合在档案中不存在时该行将报错。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>